--- a/other/states.xlsx
+++ b/other/states.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariareboredoprado/Desktop/trinity/atmo_network/other/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0064932-F339-274D-85F3-35381F3374FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25EE0C37-435B-0E42-9EE7-FD11666ED590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{63299243-8A1E-C04E-BC87-013FD0B19559}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17540" xr2:uid="{63299243-8A1E-C04E-BC87-013FD0B19559}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -201,12 +201,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAE46A"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="1" tint="0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -239,6 +233,12 @@
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -277,10 +277,10 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -289,13 +289,13 @@
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -694,10 +694,10 @@
       <c r="G6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="11" t="s">
+      <c r="H6" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -734,10 +734,10 @@
       <c r="G8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="11" t="s">
+      <c r="H8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -774,10 +774,10 @@
       <c r="G10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="11" t="s">
+      <c r="H10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -814,10 +814,10 @@
       <c r="G12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="11" t="s">
+      <c r="H12" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -851,13 +851,13 @@
       <c r="F14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="11" t="s">
+      <c r="H14" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -891,13 +891,13 @@
       <c r="F16" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="11" t="s">
+      <c r="H16" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -925,19 +925,19 @@
       <c r="D18" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="16" t="s">
         <v>9</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="H18" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="11" t="s">
+      <c r="H18" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -968,16 +968,16 @@
       <c r="E20" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="H20" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I20" s="11" t="s">
+      <c r="H20" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1014,10 +1014,10 @@
       <c r="G22" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" s="11" t="s">
+      <c r="H22" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1054,10 +1054,10 @@
       <c r="G24" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H24" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="11" t="s">
+      <c r="H24" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1094,10 +1094,10 @@
       <c r="G26" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H26" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I26" s="11" t="s">
+      <c r="H26" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1134,10 +1134,10 @@
       <c r="G28" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H28" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" s="11" t="s">
+      <c r="H28" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1174,10 +1174,10 @@
       <c r="G30" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H30" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I30" s="11" t="s">
+      <c r="H30" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1214,10 +1214,10 @@
       <c r="G32" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H32" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32" s="11" t="s">
+      <c r="H32" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1254,10 +1254,10 @@
       <c r="G34" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H34" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" s="11" t="s">
+      <c r="H34" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1294,10 +1294,10 @@
       <c r="G36" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H36" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" s="11" t="s">
+      <c r="H36" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1331,13 +1331,13 @@
       <c r="F38" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G38" s="12" t="s">
+      <c r="G38" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H38" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I38" s="11" t="s">
+      <c r="H38" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       <c r="D40" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F40" s="9" t="s">
@@ -1374,10 +1374,10 @@
       <c r="G40" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H40" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I40" s="11" t="s">
+      <c r="H40" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1414,10 +1414,10 @@
       <c r="G42" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H42" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I42" s="11" t="s">
+      <c r="H42" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I42" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1451,13 +1451,13 @@
       <c r="F44" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G44" s="13" t="s">
+      <c r="G44" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I44" s="11" t="s">
+      <c r="H44" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1491,13 +1491,13 @@
       <c r="F46" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G46" s="13" t="s">
+      <c r="G46" s="12" t="s">
         <v>18</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I46" s="11" t="s">
+      <c r="I46" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1525,19 +1525,19 @@
       <c r="D48" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="E48" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F48" s="14" t="s">
+      <c r="F48" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G48" s="13" t="s">
+      <c r="G48" s="12" t="s">
         <v>18</v>
       </c>
       <c r="H48" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I48" s="11" t="s">
+      <c r="I48" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1568,16 +1568,16 @@
       <c r="E50" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F50" s="14" t="s">
+      <c r="F50" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G50" s="13" t="s">
+      <c r="G50" s="12" t="s">
         <v>18</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I50" s="11" t="s">
+      <c r="I50" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1608,16 +1608,16 @@
       <c r="E52" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F52" s="16" t="s">
+      <c r="F52" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G52" s="13" t="s">
+      <c r="G52" s="12" t="s">
         <v>18</v>
       </c>
       <c r="H52" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I52" s="11" t="s">
+      <c r="I52" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1651,13 +1651,13 @@
       <c r="F54" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G54" s="13" t="s">
+      <c r="G54" s="12" t="s">
         <v>18</v>
       </c>
       <c r="H54" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I54" s="11" t="s">
+      <c r="I54" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1685,19 +1685,19 @@
       <c r="D56" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E56" s="16" t="s">
+      <c r="E56" s="15" t="s">
         <v>13</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G56" s="13" t="s">
+      <c r="G56" s="12" t="s">
         <v>18</v>
       </c>
       <c r="H56" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I56" s="11" t="s">
+      <c r="I56" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1731,13 +1731,13 @@
       <c r="F58" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G58" s="11" t="s">
+      <c r="G58" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I58" s="11" t="s">
+      <c r="I58" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1771,13 +1771,13 @@
       <c r="F60" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G60" s="11" t="s">
+      <c r="G60" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H60" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I60" s="11" t="s">
+      <c r="I60" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1811,13 +1811,13 @@
       <c r="F62" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G62" s="11" t="s">
+      <c r="G62" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="I62" s="11" t="s">
+      <c r="I62" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1845,19 +1845,19 @@
       <c r="D64" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="E64" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G64" s="11" t="s">
+      <c r="G64" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I64" s="11" t="s">
+      <c r="I64" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1885,19 +1885,19 @@
       <c r="D66" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E66" s="10" t="s">
+      <c r="E66" s="16" t="s">
         <v>9</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G66" s="11" t="s">
+      <c r="G66" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H66" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I66" s="11" t="s">
+      <c r="I66" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1931,13 +1931,13 @@
       <c r="F68" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G68" s="11" t="s">
+      <c r="G68" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H68" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I68" s="11" t="s">
+      <c r="I68" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1971,13 +1971,13 @@
       <c r="F70" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G70" s="11" t="s">
+      <c r="G70" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H70" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I70" s="11" t="s">
+      <c r="I70" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2011,13 +2011,13 @@
       <c r="F72" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G72" s="11" t="s">
+      <c r="G72" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H72" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I72" s="11" t="s">
+      <c r="I72" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2045,19 +2045,19 @@
       <c r="D74" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E74" s="5" t="s">
+      <c r="E74" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G74" s="11" t="s">
+      <c r="G74" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I74" s="11" t="s">
+      <c r="I74" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2091,13 +2091,13 @@
       <c r="F76" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G76" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H76" s="12" t="s">
+      <c r="G76" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H76" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I76" s="11" t="s">
+      <c r="I76" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2125,19 +2125,19 @@
       <c r="D78" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E78" s="16" t="s">
+      <c r="E78" s="15" t="s">
         <v>13</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G78" s="15" t="s">
+      <c r="G78" s="14" t="s">
         <v>19</v>
       </c>
       <c r="H78" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I78" s="11" t="s">
+      <c r="I78" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2171,13 +2171,13 @@
       <c r="F80" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G80" s="11" t="s">
+      <c r="G80" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H80" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I80" s="11" t="s">
+      <c r="I80" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2211,13 +2211,13 @@
       <c r="F82" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G82" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H82" s="12" t="s">
+      <c r="G82" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H82" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I82" s="11" t="s">
+      <c r="I82" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2251,13 +2251,13 @@
       <c r="F84" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G84" s="11" t="s">
+      <c r="G84" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I84" s="11" t="s">
+      <c r="I84" s="10" t="s">
         <v>14</v>
       </c>
     </row>
